--- a/Outputs/Recycling_Plot_Data/Repeal/01b_Geofacet_RegionMass_2050_data_Repeal.xlsx
+++ b/Outputs/Recycling_Plot_Data/Repeal/01b_Geofacet_RegionMass_2050_data_Repeal.xlsx
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.5845245226777597</v>
+        <v>0.584029460298372</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>1.094560404406895</v>
+        <v>1.093633367717815</v>
       </c>
     </row>
     <row r="5">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.0676166079199273</v>
+        <v>0.06755934011078625</v>
       </c>
     </row>
     <row r="28">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.5477544793648994</v>
+        <v>0.5476838187546399</v>
       </c>
     </row>
     <row r="30">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>1.906177861967587</v>
+        <v>1.904563426796315</v>
       </c>
     </row>
     <row r="34">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="D34">
-        <v>1.191317809708739</v>
+        <v>1.190308824445332</v>
       </c>
     </row>
     <row r="35">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D39">
-        <v>2.64973644832911</v>
+        <v>2.647492257059168</v>
       </c>
     </row>
     <row r="40">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>2.897704649561412</v>
+        <v>2.895250441905584</v>
       </c>
     </row>
     <row r="41">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D45">
-        <v>0.1551318175991474</v>
+        <v>0.1550004288827467</v>
       </c>
     </row>
     <row r="46">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="D46">
-        <v>0.3577298435455472</v>
+        <v>0.3574268646615949</v>
       </c>
     </row>
     <row r="47">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="D51">
-        <v>2.914855372273894</v>
+        <v>2.91238663883298</v>
       </c>
     </row>
     <row r="52">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D52">
-        <v>0.9477517932895018</v>
+        <v>0.9469490959865631</v>
       </c>
     </row>
     <row r="53">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="D56">
-        <v>1.85956732274255</v>
+        <v>1.850718445057074</v>
       </c>
     </row>
     <row r="57">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="D57">
-        <v>2.15003844005531</v>
+        <v>2.148217467444901</v>
       </c>
     </row>
     <row r="58">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D58">
-        <v>0.09418670599324755</v>
+        <v>0.09410693466977575</v>
       </c>
     </row>
     <row r="59">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D59">
-        <v>0.9776773872413603</v>
+        <v>0.9700189022977317</v>
       </c>
     </row>
     <row r="60">
